--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T10:56:37+00:00</t>
+    <t>2025-01-17T11:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T11:40:58+00:00</t>
+    <t>2025-01-21T12:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-21T12:24:15+00:00</t>
+    <t>2025-01-23T11:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T11:46:49+00:00</t>
+    <t>2025-01-24T11:26:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T11:26:43+00:00</t>
+    <t>2025-01-29T08:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T08:49:29+00:00</t>
+    <t>2025-01-29T12:34:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationpregnancystatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T12:34:29+00:00</t>
+    <t>2025-02-03T12:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
